--- a/prix/laiton.xlsx
+++ b/prix/laiton.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B1FD1F-2959-42DC-A3DE-671637E1C461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FEB1B9-7B60-4999-8C4E-1C62C43B4C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2BA8A27F-C677-4342-8A29-D0C4A22FC515}"/>
   </bookViews>
@@ -1677,7 +1677,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="16">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1717,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="16">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1737,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="16">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1897,7 +1897,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="16">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2011,13 +2011,13 @@
         <v>271</v>
       </c>
       <c r="D20" s="19">
-        <v>9.85</v>
+        <v>10.41</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>36</v>
       </c>
       <c r="F20" s="18">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2131,7 +2131,7 @@
         <v>271</v>
       </c>
       <c r="D26" s="19">
-        <v>14.94</v>
+        <v>16.14</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>48</v>
@@ -2157,7 +2157,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="18">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2297,7 +2297,7 @@
         <v>64</v>
       </c>
       <c r="F34" s="18">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2317,7 +2317,7 @@
         <v>66</v>
       </c>
       <c r="F35" s="18">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2337,7 +2337,7 @@
         <v>68</v>
       </c>
       <c r="F36" s="18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2477,7 +2477,7 @@
         <v>82</v>
       </c>
       <c r="F43" s="18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2497,7 +2497,7 @@
         <v>84</v>
       </c>
       <c r="F44" s="18">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2517,7 +2517,7 @@
         <v>86</v>
       </c>
       <c r="F45" s="18">
-        <v>16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2537,7 +2537,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="18">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2597,7 +2597,7 @@
         <v>94</v>
       </c>
       <c r="F49" s="18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2657,7 +2657,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="18">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2677,7 +2677,7 @@
         <v>102</v>
       </c>
       <c r="F53" s="18">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2697,7 +2697,7 @@
         <v>104</v>
       </c>
       <c r="F54" s="18">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2757,7 +2757,7 @@
         <v>110</v>
       </c>
       <c r="F57" s="18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2852,7 +2852,7 @@
         <v>120</v>
       </c>
       <c r="F62" s="18">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2872,7 +2872,7 @@
         <v>122</v>
       </c>
       <c r="F63" s="18">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2912,7 +2912,7 @@
         <v>126</v>
       </c>
       <c r="F65" s="18">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2932,7 +2932,7 @@
         <v>128</v>
       </c>
       <c r="F66" s="18">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2952,7 +2952,7 @@
         <v>130</v>
       </c>
       <c r="F67" s="18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -3067,7 +3067,7 @@
         <v>141</v>
       </c>
       <c r="F73" s="18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3087,7 +3087,7 @@
         <v>143</v>
       </c>
       <c r="F74" s="18">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3207,7 +3207,7 @@
         <v>155</v>
       </c>
       <c r="F80" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3247,7 +3247,7 @@
         <v>159</v>
       </c>
       <c r="F82" s="18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3422,7 +3422,7 @@
         <v>176</v>
       </c>
       <c r="F91" s="18">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3442,7 +3442,7 @@
         <v>178</v>
       </c>
       <c r="F92" s="18">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3456,13 +3456,13 @@
         <v>309</v>
       </c>
       <c r="D93" s="19">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>180</v>
       </c>
       <c r="F93" s="18">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3602,7 +3602,7 @@
         <v>194</v>
       </c>
       <c r="F100" s="18">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -3622,7 +3622,7 @@
         <v>196</v>
       </c>
       <c r="F101" s="18">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
@@ -3642,7 +3642,7 @@
         <v>198</v>
       </c>
       <c r="F102" s="18">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
@@ -3722,7 +3722,7 @@
         <v>206</v>
       </c>
       <c r="F106" s="18">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
@@ -3742,7 +3742,7 @@
         <v>208</v>
       </c>
       <c r="F107" s="18">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>210</v>
       </c>
       <c r="F108" s="18">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
@@ -3976,7 +3976,7 @@
         <v>230</v>
       </c>
       <c r="F118" s="22">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -4016,7 +4016,7 @@
         <v>234</v>
       </c>
       <c r="F120" s="22">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4036,7 +4036,7 @@
         <v>236</v>
       </c>
       <c r="F121" s="22">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/laiton.xlsx
+++ b/prix/laiton.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FEB1B9-7B60-4999-8C4E-1C62C43B4C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB9B78B-A4D3-4057-B084-C92D3A526CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2BA8A27F-C677-4342-8A29-D0C4A22FC515}"/>
   </bookViews>
@@ -1231,6 +1231,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1256,9 +1259,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1650,13 +1650,13 @@
       <c r="C2" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="16">
         <v>1.03</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1670,13 +1670,13 @@
       <c r="C3" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <v>1.73</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="17">
         <v>-1</v>
       </c>
     </row>
@@ -1690,14 +1690,14 @@
       <c r="C4" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>1.82</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="16">
-        <v>18</v>
+      <c r="F4" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1710,14 +1710,14 @@
       <c r="C5" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>0.81</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="16">
-        <v>55</v>
+      <c r="F5" s="17">
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1730,14 +1730,14 @@
       <c r="C6" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <v>1.03</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="16">
-        <v>14</v>
+      <c r="F6" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1750,13 +1750,13 @@
       <c r="C7" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>2.09</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="17">
         <v>15</v>
       </c>
     </row>
@@ -1770,13 +1770,13 @@
       <c r="C8" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>3.5500000000000003</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="17">
         <v>6</v>
       </c>
     </row>
@@ -1790,13 +1790,13 @@
       <c r="C9" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <v>6.9</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="17">
         <v>0</v>
       </c>
     </row>
@@ -1810,13 +1810,13 @@
       <c r="C10" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <v>0.82000000000000006</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="17">
         <v>15</v>
       </c>
     </row>
@@ -1830,14 +1830,14 @@
       <c r="C11" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <v>1.19</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="16">
-        <v>12</v>
+      <c r="F11" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1850,14 +1850,14 @@
       <c r="C12" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <v>0.54</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="16">
-        <v>42</v>
+      <c r="F12" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1870,14 +1870,14 @@
       <c r="C13" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D13" s="17">
-        <v>1.1500000000000001</v>
+      <c r="D13" s="16">
+        <v>0.64</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="16">
-        <v>19</v>
+      <c r="F13" s="17">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1890,14 +1890,14 @@
       <c r="C14" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="16">
         <v>2.15</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="16">
-        <v>15</v>
+      <c r="F14" s="17">
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1910,14 +1910,14 @@
       <c r="C15" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <v>1.69</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="16">
-        <v>18</v>
+      <c r="F15" s="17">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1930,14 +1930,14 @@
       <c r="C16" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="16">
         <v>4.6900000000000004</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="16">
-        <v>7</v>
+      <c r="F16" s="17">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1950,14 +1950,14 @@
       <c r="C17" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="16">
         <v>5.9</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="16">
-        <v>6</v>
+      <c r="F17" s="17">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1970,13 +1970,13 @@
       <c r="C18" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="18">
         <v>7.2700000000000005</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="19">
         <v>0</v>
       </c>
     </row>
@@ -1990,14 +1990,14 @@
       <c r="C19" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="18">
         <v>6.63</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="18">
-        <v>5</v>
+      <c r="F19" s="19">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2010,14 +2010,14 @@
       <c r="C20" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="18">
         <v>10.41</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="18">
-        <v>2</v>
+      <c r="F20" s="19">
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2030,14 +2030,14 @@
       <c r="C21" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="18">
         <v>13.950000000000001</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="18">
-        <v>8</v>
+      <c r="F21" s="19">
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2050,13 +2050,13 @@
       <c r="C22" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="18">
         <v>23.04</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <v>6</v>
       </c>
     </row>
@@ -2070,13 +2070,13 @@
       <c r="C23" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="18">
         <v>34.5</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <v>1</v>
       </c>
     </row>
@@ -2090,13 +2090,13 @@
       <c r="C24" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="18">
         <v>5.15</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="19">
         <v>5</v>
       </c>
     </row>
@@ -2110,13 +2110,13 @@
       <c r="C25" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="18">
         <v>8.7799999999999994</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="19">
         <v>9</v>
       </c>
     </row>
@@ -2130,14 +2130,14 @@
       <c r="C26" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="18">
         <v>16.14</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="18">
-        <v>3</v>
+      <c r="F26" s="19">
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2150,14 +2150,14 @@
       <c r="C27" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="18">
         <v>27.09</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="18">
-        <v>4</v>
+      <c r="F27" s="19">
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2170,13 +2170,13 @@
       <c r="C28" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="18">
         <v>53.88</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="19">
         <v>5</v>
       </c>
     </row>
@@ -2190,13 +2190,13 @@
       <c r="C29" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="18">
         <v>53.88</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2210,13 +2210,13 @@
       <c r="C30" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="18">
         <v>10.620000000000001</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="19">
         <v>20</v>
       </c>
     </row>
@@ -2230,13 +2230,13 @@
       <c r="C31" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="18">
         <v>16.13</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="19">
         <v>4</v>
       </c>
     </row>
@@ -2250,13 +2250,13 @@
       <c r="C32" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="18">
         <v>2.86</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2270,14 +2270,14 @@
       <c r="C33" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="18">
         <v>2.04</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="18">
-        <v>12</v>
+      <c r="F33" s="19">
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2290,14 +2290,14 @@
       <c r="C34" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="18">
         <v>3.11</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="18">
-        <v>19</v>
+      <c r="F34" s="19">
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2310,14 +2310,14 @@
       <c r="C35" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="18">
         <v>4.22</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="18">
-        <v>16</v>
+      <c r="F35" s="19">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2330,14 +2330,14 @@
       <c r="C36" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="18">
         <v>7.51</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="18">
-        <v>8</v>
+      <c r="F36" s="19">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2350,13 +2350,13 @@
       <c r="C37" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="18">
         <v>15.52</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="19">
         <v>7</v>
       </c>
     </row>
@@ -2370,13 +2370,13 @@
       <c r="C38" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="18">
         <v>17.64</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="19">
         <v>27</v>
       </c>
     </row>
@@ -2390,13 +2390,13 @@
       <c r="C39" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="18">
         <v>10.1</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2410,14 +2410,14 @@
       <c r="C40" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="18">
         <v>6.15</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="18">
-        <v>10</v>
+      <c r="F40" s="19">
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2430,13 +2430,13 @@
       <c r="C41" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="18">
         <v>0.91</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="19">
         <v>10</v>
       </c>
     </row>
@@ -2450,13 +2450,13 @@
       <c r="C42" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="18">
         <v>1.98</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="19">
         <v>15</v>
       </c>
     </row>
@@ -2470,14 +2470,14 @@
       <c r="C43" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="18">
         <v>1.06</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="F43" s="18">
-        <v>5</v>
+      <c r="F43" s="19">
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2490,14 +2490,14 @@
       <c r="C44" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="18">
         <v>1.26</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F44" s="18">
-        <v>45</v>
+      <c r="F44" s="19">
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2510,14 +2510,14 @@
       <c r="C45" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="18">
         <v>1.57</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F45" s="18">
-        <v>-1</v>
+      <c r="F45" s="19">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2530,14 +2530,14 @@
       <c r="C46" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="18">
         <v>2.95</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F46" s="18">
-        <v>25</v>
+      <c r="F46" s="19">
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2550,13 +2550,13 @@
       <c r="C47" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="18">
         <v>6.49</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="19">
         <v>4</v>
       </c>
     </row>
@@ -2570,13 +2570,13 @@
       <c r="C48" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="18">
         <v>6.44</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="19">
         <v>6</v>
       </c>
     </row>
@@ -2590,13 +2590,13 @@
       <c r="C49" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="18">
         <v>1.1100000000000001</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="19">
         <v>9</v>
       </c>
     </row>
@@ -2610,13 +2610,13 @@
       <c r="C50" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="18">
         <v>1.62</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2630,13 +2630,13 @@
       <c r="C51" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="18">
         <v>1.98</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="19">
         <v>14</v>
       </c>
     </row>
@@ -2650,14 +2650,14 @@
       <c r="C52" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="18">
         <v>1.22</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F52" s="18">
-        <v>23</v>
+      <c r="F52" s="19">
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2670,14 +2670,14 @@
       <c r="C53" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="18">
         <v>1.94</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="18">
-        <v>28</v>
+      <c r="F53" s="19">
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2690,14 +2690,14 @@
       <c r="C54" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="18">
         <v>2.57</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="18">
-        <v>25</v>
+      <c r="F54" s="19">
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2710,13 +2710,13 @@
       <c r="C55" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="18">
         <v>5.66</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="18">
+      <c r="F55" s="19">
         <v>15</v>
       </c>
     </row>
@@ -2730,13 +2730,13 @@
       <c r="C56" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="18">
         <v>7.0200000000000005</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="F56" s="18">
+      <c r="F56" s="19">
         <v>6</v>
       </c>
     </row>
@@ -2750,13 +2750,13 @@
       <c r="C57" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="18">
         <v>5.45</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="18">
+      <c r="F57" s="19">
         <v>6</v>
       </c>
     </row>
@@ -2765,13 +2765,13 @@
         <v>113</v>
       </c>
       <c r="C58" s="7"/>
-      <c r="D58" s="19">
+      <c r="D58" s="18">
         <v>0</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="18">
+      <c r="F58" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2785,13 +2785,13 @@
       <c r="C59" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="18">
         <v>0.65</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="18">
+      <c r="F59" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2805,13 +2805,13 @@
       <c r="C60" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="18">
         <v>0.65</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="18">
+      <c r="F60" s="19">
         <v>4</v>
       </c>
     </row>
@@ -2825,13 +2825,13 @@
       <c r="C61" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="18">
         <v>0.63</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="18">
+      <c r="F61" s="19">
         <v>-1</v>
       </c>
     </row>
@@ -2845,14 +2845,14 @@
       <c r="C62" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="18">
         <v>1.22</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="18">
-        <v>50</v>
+      <c r="F62" s="19">
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2865,14 +2865,14 @@
       <c r="C63" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="18">
         <v>1.21</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="18">
-        <v>13</v>
+      <c r="F63" s="19">
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2885,14 +2885,14 @@
       <c r="C64" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="18">
         <v>2.44</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F64" s="18">
-        <v>27</v>
+      <c r="F64" s="19">
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2905,14 +2905,14 @@
       <c r="C65" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="18">
         <v>2.13</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="18">
-        <v>36</v>
+      <c r="F65" s="19">
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2925,14 +2925,14 @@
       <c r="C66" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="18">
         <v>4.1100000000000003</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="18">
-        <v>13</v>
+      <c r="F66" s="19">
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2945,14 +2945,14 @@
       <c r="C67" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="18">
         <v>5.54</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F67" s="18">
-        <v>8</v>
+      <c r="F67" s="19">
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2960,13 +2960,13 @@
         <v>113</v>
       </c>
       <c r="C68" s="7"/>
-      <c r="D68" s="19">
+      <c r="D68" s="18">
         <v>0</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="18">
+      <c r="F68" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2980,13 +2980,13 @@
       <c r="C69" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="D69" s="19">
+      <c r="D69" s="18">
         <v>4.9400000000000004</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F69" s="18">
+      <c r="F69" s="19">
         <v>14</v>
       </c>
     </row>
@@ -3000,13 +3000,13 @@
       <c r="C70" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="D70" s="19">
+      <c r="D70" s="18">
         <v>1.21</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="F70" s="18">
+      <c r="F70" s="19">
         <v>10</v>
       </c>
     </row>
@@ -3020,13 +3020,13 @@
       <c r="C71" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="D71" s="19">
+      <c r="D71" s="18">
         <v>1.0900000000000001</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="F71" s="18">
+      <c r="F71" s="19">
         <v>0</v>
       </c>
     </row>
@@ -3040,13 +3040,13 @@
       <c r="C72" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="D72" s="19">
+      <c r="D72" s="18">
         <v>1.6500000000000001</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="F72" s="18">
+      <c r="F72" s="19">
         <v>0</v>
       </c>
     </row>
@@ -3060,14 +3060,14 @@
       <c r="C73" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D73" s="19">
+      <c r="D73" s="18">
         <v>1.1400000000000001</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F73" s="18">
-        <v>7</v>
+      <c r="F73" s="19">
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3080,14 +3080,14 @@
       <c r="C74" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D74" s="19">
+      <c r="D74" s="18">
         <v>1.6</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="F74" s="18">
-        <v>18</v>
+      <c r="F74" s="19">
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3100,13 +3100,13 @@
       <c r="C75" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="D75" s="19">
+      <c r="D75" s="18">
         <v>2.73</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="F75" s="18">
+      <c r="F75" s="19">
         <v>16</v>
       </c>
     </row>
@@ -3120,14 +3120,14 @@
       <c r="C76" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="D76" s="19">
+      <c r="D76" s="18">
         <v>2.71</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="F76" s="18">
-        <v>15</v>
+      <c r="F76" s="19">
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3140,13 +3140,13 @@
       <c r="C77" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="D77" s="19">
+      <c r="D77" s="18">
         <v>5.9</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="F77" s="18">
+      <c r="F77" s="19">
         <v>14</v>
       </c>
     </row>
@@ -3160,14 +3160,14 @@
       <c r="C78" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="D78" s="19">
+      <c r="D78" s="18">
         <v>7.7700000000000005</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="F78" s="18">
-        <v>2</v>
+      <c r="F78" s="19">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3180,13 +3180,13 @@
       <c r="C79" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="D79" s="19">
+      <c r="D79" s="18">
         <v>1.0900000000000001</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F79" s="18">
+      <c r="F79" s="19">
         <v>9</v>
       </c>
     </row>
@@ -3200,13 +3200,13 @@
       <c r="C80" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D80" s="19">
+      <c r="D80" s="18">
         <v>1.1100000000000001</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F80" s="18">
+      <c r="F80" s="19">
         <v>0</v>
       </c>
     </row>
@@ -3220,13 +3220,13 @@
       <c r="C81" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="D81" s="19">
+      <c r="D81" s="18">
         <v>2.57</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="F81" s="18">
+      <c r="F81" s="19">
         <v>27</v>
       </c>
     </row>
@@ -3240,14 +3240,14 @@
       <c r="C82" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="D82" s="19">
+      <c r="D82" s="18">
         <v>2.9</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="F82" s="18">
-        <v>8</v>
+      <c r="F82" s="19">
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3260,14 +3260,14 @@
       <c r="C83" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="D83" s="19">
+      <c r="D83" s="18">
         <v>3.44</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="F83" s="18">
-        <v>21</v>
+      <c r="F83" s="19">
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3280,13 +3280,13 @@
       <c r="C84" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="D84" s="19">
+      <c r="D84" s="18">
         <v>3.44</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="F84" s="18">
+      <c r="F84" s="19">
         <v>18</v>
       </c>
     </row>
@@ -3300,13 +3300,13 @@
       <c r="C85" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="D85" s="19">
+      <c r="D85" s="18">
         <v>6.17</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="F85" s="18">
+      <c r="F85" s="19">
         <v>21</v>
       </c>
     </row>
@@ -3320,13 +3320,13 @@
       <c r="C86" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D86" s="19">
+      <c r="D86" s="18">
         <v>5.74</v>
       </c>
       <c r="E86" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="F86" s="18">
+      <c r="F86" s="19">
         <v>4</v>
       </c>
     </row>
@@ -3340,13 +3340,13 @@
       <c r="C87" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="D87" s="19">
+      <c r="D87" s="18">
         <v>10.84</v>
       </c>
       <c r="E87" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="F87" s="18">
+      <c r="F87" s="19">
         <v>0</v>
       </c>
     </row>
@@ -3355,13 +3355,13 @@
         <v>113</v>
       </c>
       <c r="C88" s="7"/>
-      <c r="D88" s="19">
+      <c r="D88" s="18">
         <v>0</v>
       </c>
       <c r="E88" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="F88" s="18">
+      <c r="F88" s="19">
         <v>0</v>
       </c>
     </row>
@@ -3375,13 +3375,13 @@
       <c r="C89" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D89" s="19">
+      <c r="D89" s="18">
         <v>0.82000000000000006</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="F89" s="18">
+      <c r="F89" s="19">
         <v>8</v>
       </c>
     </row>
@@ -3395,13 +3395,13 @@
       <c r="C90" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D90" s="19">
+      <c r="D90" s="18">
         <v>2.52</v>
       </c>
       <c r="E90" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="F90" s="18">
+      <c r="F90" s="19">
         <v>8</v>
       </c>
     </row>
@@ -3415,14 +3415,14 @@
       <c r="C91" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D91" s="19">
+      <c r="D91" s="18">
         <v>1.26</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="F91" s="18">
-        <v>34</v>
+      <c r="F91" s="19">
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3435,13 +3435,13 @@
       <c r="C92" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D92" s="19">
+      <c r="D92" s="18">
         <v>1.74</v>
       </c>
       <c r="E92" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="F92" s="18">
+      <c r="F92" s="19">
         <v>49</v>
       </c>
     </row>
@@ -3455,14 +3455,14 @@
       <c r="C93" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="D93" s="19">
-        <v>2.86</v>
+      <c r="D93" s="18">
+        <v>2.9</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="F93" s="18">
-        <v>13</v>
+      <c r="F93" s="19">
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3475,14 +3475,14 @@
       <c r="C94" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D94" s="19">
+      <c r="D94" s="18">
         <v>4.09</v>
       </c>
       <c r="E94" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F94" s="18">
-        <v>9</v>
+      <c r="F94" s="19">
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3495,13 +3495,13 @@
       <c r="C95" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D95" s="19">
+      <c r="D95" s="18">
         <v>7.57</v>
       </c>
       <c r="E95" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F95" s="18">
+      <c r="F95" s="19">
         <v>5</v>
       </c>
     </row>
@@ -3515,13 +3515,13 @@
       <c r="C96" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D96" s="19">
+      <c r="D96" s="18">
         <v>9.75</v>
       </c>
       <c r="E96" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="F96" s="18">
+      <c r="F96" s="19">
         <v>13</v>
       </c>
     </row>
@@ -3535,13 +3535,13 @@
       <c r="C97" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D97" s="19">
+      <c r="D97" s="18">
         <v>8.42</v>
       </c>
       <c r="E97" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="F97" s="18">
+      <c r="F97" s="19">
         <v>10</v>
       </c>
     </row>
@@ -3555,13 +3555,13 @@
       <c r="C98" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D98" s="19">
+      <c r="D98" s="18">
         <v>6.95</v>
       </c>
       <c r="E98" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="F98" s="18">
+      <c r="F98" s="19">
         <v>7</v>
       </c>
     </row>
@@ -3575,13 +3575,13 @@
       <c r="C99" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D99" s="19">
+      <c r="D99" s="18">
         <v>1.69</v>
       </c>
       <c r="E99" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="F99" s="18">
+      <c r="F99" s="19">
         <v>34</v>
       </c>
     </row>
@@ -3595,14 +3595,14 @@
       <c r="C100" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D100" s="19">
+      <c r="D100" s="18">
         <v>2.73</v>
       </c>
       <c r="E100" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="F100" s="18">
-        <v>36</v>
+      <c r="F100" s="19">
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -3615,14 +3615,14 @@
       <c r="C101" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D101" s="19">
+      <c r="D101" s="18">
         <v>3.56</v>
       </c>
       <c r="E101" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="F101" s="18">
-        <v>17</v>
+      <c r="F101" s="19">
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
@@ -3635,13 +3635,13 @@
       <c r="C102" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D102" s="19">
+      <c r="D102" s="18">
         <v>7.36</v>
       </c>
       <c r="E102" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="F102" s="18">
+      <c r="F102" s="19">
         <v>14</v>
       </c>
     </row>
@@ -3655,13 +3655,13 @@
       <c r="C103" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D103" s="19">
+      <c r="D103" s="18">
         <v>15.58</v>
       </c>
       <c r="E103" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="F103" s="18">
+      <c r="F103" s="19">
         <v>4</v>
       </c>
     </row>
@@ -3675,13 +3675,13 @@
       <c r="C104" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D104" s="19">
+      <c r="D104" s="18">
         <v>18.830000000000002</v>
       </c>
       <c r="E104" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="F104" s="18">
+      <c r="F104" s="19">
         <v>4</v>
       </c>
     </row>
@@ -3695,14 +3695,14 @@
       <c r="C105" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D105" s="19">
+      <c r="D105" s="18">
         <v>1.77</v>
       </c>
       <c r="E105" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="F105" s="18">
-        <v>27</v>
+      <c r="F105" s="19">
+        <v>25</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -3715,14 +3715,14 @@
       <c r="C106" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D106" s="19">
+      <c r="D106" s="18">
         <v>2.11</v>
       </c>
       <c r="E106" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="F106" s="18">
-        <v>20</v>
+      <c r="F106" s="19">
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
@@ -3735,14 +3735,14 @@
       <c r="C107" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D107" s="19">
+      <c r="D107" s="18">
         <v>3.92</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="F107" s="18">
-        <v>3</v>
+      <c r="F107" s="19">
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -3755,14 +3755,14 @@
       <c r="C108" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D108" s="19">
-        <v>6.07</v>
+      <c r="D108" s="18">
+        <v>6.15</v>
       </c>
       <c r="E108" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="F108" s="18">
-        <v>8</v>
+      <c r="F108" s="19">
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
@@ -3775,13 +3775,13 @@
       <c r="C109" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D109" s="19">
+      <c r="D109" s="18">
         <v>14.35</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="F109" s="18">
+      <c r="F109" s="19">
         <v>3</v>
       </c>
     </row>
@@ -3795,13 +3795,13 @@
       <c r="C110" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D110" s="19">
+      <c r="D110" s="18">
         <v>17.420000000000002</v>
       </c>
       <c r="E110" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="F110" s="18">
+      <c r="F110" s="19">
         <v>1</v>
       </c>
     </row>
@@ -3815,13 +3815,13 @@
       <c r="C111" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="D111" s="21">
+      <c r="D111" s="20">
         <v>6.23</v>
       </c>
       <c r="E111" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="F111" s="20">
+      <c r="F111" s="21">
         <v>0</v>
       </c>
       <c r="G111" s="2"/>
@@ -3842,14 +3842,14 @@
       <c r="C112" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D112" s="21">
+      <c r="D112" s="20">
         <v>7.5</v>
       </c>
       <c r="E112" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="F112" s="20">
-        <v>1</v>
+      <c r="F112" s="21">
+        <v>6</v>
       </c>
       <c r="G112" s="2"/>
       <c r="I112" s="2"/>
@@ -3869,14 +3869,14 @@
       <c r="C113" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D113" s="21">
+      <c r="D113" s="20">
         <v>5.76</v>
       </c>
       <c r="E113" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="F113" s="20">
-        <v>32</v>
+      <c r="F113" s="21">
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3889,13 +3889,13 @@
       <c r="C114" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="D114" s="21">
+      <c r="D114" s="20">
         <v>10.51</v>
       </c>
       <c r="E114" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="F114" s="20">
+      <c r="F114" s="21">
         <v>10</v>
       </c>
     </row>
@@ -3909,13 +3909,13 @@
       <c r="C115" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="D115" s="21">
+      <c r="D115" s="20">
         <v>10.25</v>
       </c>
       <c r="E115" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="F115" s="20">
+      <c r="F115" s="21">
         <v>0</v>
       </c>
     </row>
@@ -3929,13 +3929,13 @@
       <c r="C116" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D116" s="21">
+      <c r="D116" s="20">
         <v>7.01</v>
       </c>
       <c r="E116" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="F116" s="20">
+      <c r="F116" s="21">
         <v>8</v>
       </c>
     </row>
@@ -3949,13 +3949,13 @@
       <c r="C117" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D117" s="21">
+      <c r="D117" s="20">
         <v>15.58</v>
       </c>
       <c r="E117" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="F117" s="20">
+      <c r="F117" s="21">
         <v>0</v>
       </c>
     </row>
@@ -3969,14 +3969,14 @@
       <c r="C118" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D118" s="23">
+      <c r="D118" s="22">
         <v>1.61</v>
       </c>
       <c r="E118" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="F118" s="22">
-        <v>23</v>
+      <c r="F118" s="23">
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -3989,14 +3989,14 @@
       <c r="C119" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="D119" s="23">
+      <c r="D119" s="22">
         <v>2.35</v>
       </c>
       <c r="E119" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="F119" s="22">
-        <v>18</v>
+      <c r="F119" s="23">
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -4009,14 +4009,14 @@
       <c r="C120" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D120" s="23">
+      <c r="D120" s="22">
         <v>3.11</v>
       </c>
       <c r="E120" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="F120" s="22">
-        <v>24</v>
+      <c r="F120" s="23">
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4029,14 +4029,14 @@
       <c r="C121" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="D121" s="23">
+      <c r="D121" s="22">
         <v>5.23</v>
       </c>
       <c r="E121" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="F121" s="22">
-        <v>6</v>
+      <c r="F121" s="23">
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -4049,14 +4049,14 @@
       <c r="C122" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="D122" s="23">
+      <c r="D122" s="22">
         <v>8.7100000000000009</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="F122" s="22">
-        <v>17</v>
+      <c r="F122" s="23">
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -4069,13 +4069,13 @@
       <c r="C123" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D123" s="23">
+      <c r="D123" s="22">
         <v>2.42</v>
       </c>
       <c r="E123" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="F123" s="22">
+      <c r="F123" s="23">
         <v>10</v>
       </c>
     </row>
@@ -4089,14 +4089,14 @@
       <c r="C124" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D124" s="23">
+      <c r="D124" s="22">
         <v>3.56</v>
       </c>
       <c r="E124" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="F124" s="22">
-        <v>9</v>
+      <c r="F124" s="23">
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -4109,14 +4109,14 @@
       <c r="C125" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D125" s="23">
+      <c r="D125" s="22">
         <v>3.63</v>
       </c>
       <c r="E125" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="F125" s="22">
-        <v>17</v>
+      <c r="F125" s="23">
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -4129,14 +4129,14 @@
       <c r="C126" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="D126" s="23">
+      <c r="D126" s="22">
         <v>6.9</v>
       </c>
       <c r="E126" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="F126" s="22">
-        <v>25</v>
+      <c r="F126" s="23">
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -4149,14 +4149,14 @@
       <c r="C127" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="D127" s="23">
+      <c r="D127" s="22">
         <v>10.220000000000001</v>
       </c>
       <c r="E127" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="F127" s="22">
-        <v>11</v>
+      <c r="F127" s="23">
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -4169,13 +4169,13 @@
       <c r="C128" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="D128" s="25">
+      <c r="D128" s="24">
         <v>0.97</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="F128" s="24">
+      <c r="F128" s="25">
         <v>0</v>
       </c>
     </row>
@@ -4189,14 +4189,14 @@
       <c r="C129" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="D129" s="25">
+      <c r="D129" s="24">
         <v>2.5300000000000002</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="F129" s="24">
-        <v>6</v>
+      <c r="F129" s="25">
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -4209,13 +4209,13 @@
       <c r="C130" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="D130" s="25">
+      <c r="D130" s="24">
         <v>2.4300000000000002</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="F130" s="24">
+      <c r="F130" s="25">
         <v>8</v>
       </c>
     </row>
@@ -4229,13 +4229,13 @@
       <c r="C131" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="D131" s="25">
+      <c r="D131" s="24">
         <v>3.95</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="F131" s="24">
+      <c r="F131" s="25">
         <v>7</v>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
       <c r="C132" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="D132" s="25">
+      <c r="D132" s="24">
         <v>2.8000000000000003</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="F132" s="24">
+      <c r="F132" s="25">
         <v>3</v>
       </c>
     </row>
@@ -4269,14 +4269,14 @@
       <c r="C133" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="D133" s="25">
+      <c r="D133" s="24">
         <v>3.67</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="F133" s="24">
-        <v>6</v>
+      <c r="F133" s="25">
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -4289,13 +4289,13 @@
       <c r="C134" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="D134" s="25">
+      <c r="D134" s="24">
         <v>10.14</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="F134" s="24">
+      <c r="F134" s="25">
         <v>0</v>
       </c>
     </row>
@@ -4309,13 +4309,13 @@
       <c r="C135" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="D135" s="25">
+      <c r="D135" s="24">
         <v>12.620000000000001</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="F135" s="24">
+      <c r="F135" s="25">
         <v>0</v>
       </c>
     </row>
@@ -4329,13 +4329,13 @@
       <c r="C136" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="D136" s="25">
+      <c r="D136" s="24">
         <v>4.2</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="F136" s="24">
+      <c r="F136" s="25">
         <v>7</v>
       </c>
     </row>
@@ -4349,14 +4349,14 @@
       <c r="C137" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="D137" s="25">
+      <c r="D137" s="24">
         <v>7.51</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="F137" s="24">
-        <v>3</v>
+      <c r="F137" s="25">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/prix/laiton.xlsx
+++ b/prix/laiton.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB9B78B-A4D3-4057-B084-C92D3A526CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0445A7C-A85F-4DC5-9F35-9AD48C32332D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2BA8A27F-C677-4342-8A29-D0C4A22FC515}"/>
+    <workbookView xWindow="23124" yWindow="84" windowWidth="19116" windowHeight="10884" xr2:uid="{2BA8A27F-C677-4342-8A29-D0C4A22FC515}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1697,7 +1697,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="17">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1717,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="17">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1737,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="17">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="17">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1877,7 +1877,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="17">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1897,7 +1897,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="17">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1971,7 +1971,7 @@
         <v>269</v>
       </c>
       <c r="D18" s="18">
-        <v>7.2700000000000005</v>
+        <v>22.86</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>32</v>
@@ -2017,7 +2017,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2151,13 +2151,13 @@
         <v>272</v>
       </c>
       <c r="D27" s="18">
-        <v>27.09</v>
+        <v>22.86</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>50</v>
       </c>
       <c r="F27" s="19">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2217,7 +2217,7 @@
         <v>56</v>
       </c>
       <c r="F30" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2237,7 +2237,7 @@
         <v>58</v>
       </c>
       <c r="F31" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2277,7 +2277,7 @@
         <v>62</v>
       </c>
       <c r="F33" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2297,7 +2297,7 @@
         <v>64</v>
       </c>
       <c r="F34" s="19">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2311,13 +2311,13 @@
         <v>290</v>
       </c>
       <c r="D35" s="18">
-        <v>4.22</v>
+        <v>4.03</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>66</v>
       </c>
       <c r="F35" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2337,7 +2337,7 @@
         <v>68</v>
       </c>
       <c r="F36" s="19">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2417,7 +2417,7 @@
         <v>76</v>
       </c>
       <c r="F40" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2457,7 +2457,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="19">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2477,7 +2477,7 @@
         <v>82</v>
       </c>
       <c r="F43" s="19">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2497,7 +2497,7 @@
         <v>84</v>
       </c>
       <c r="F44" s="19">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2517,7 +2517,7 @@
         <v>86</v>
       </c>
       <c r="F45" s="19">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2537,7 +2537,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="19">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2557,7 +2557,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2657,7 +2657,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="19">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2677,7 +2677,7 @@
         <v>102</v>
       </c>
       <c r="F53" s="19">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2697,7 +2697,7 @@
         <v>104</v>
       </c>
       <c r="F54" s="19">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2852,7 +2852,7 @@
         <v>120</v>
       </c>
       <c r="F62" s="19">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2872,7 +2872,7 @@
         <v>122</v>
       </c>
       <c r="F63" s="19">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2912,7 +2912,7 @@
         <v>126</v>
       </c>
       <c r="F65" s="19">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2952,7 +2952,7 @@
         <v>130</v>
       </c>
       <c r="F67" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2987,7 +2987,7 @@
         <v>133</v>
       </c>
       <c r="F69" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -3007,7 +3007,7 @@
         <v>135</v>
       </c>
       <c r="F70" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -3067,7 +3067,7 @@
         <v>141</v>
       </c>
       <c r="F73" s="19">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3087,7 +3087,7 @@
         <v>143</v>
       </c>
       <c r="F74" s="19">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3127,7 +3127,7 @@
         <v>147</v>
       </c>
       <c r="F76" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3147,7 +3147,7 @@
         <v>149</v>
       </c>
       <c r="F77" s="19">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3167,7 +3167,7 @@
         <v>151</v>
       </c>
       <c r="F78" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3227,7 +3227,7 @@
         <v>157</v>
       </c>
       <c r="F81" s="19">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3247,7 +3247,7 @@
         <v>159</v>
       </c>
       <c r="F82" s="19">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3267,7 +3267,7 @@
         <v>161</v>
       </c>
       <c r="F83" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3347,7 +3347,7 @@
         <v>169</v>
       </c>
       <c r="F87" s="19">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3422,7 +3422,7 @@
         <v>176</v>
       </c>
       <c r="F91" s="19">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3442,7 +3442,7 @@
         <v>178</v>
       </c>
       <c r="F92" s="19">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3462,7 +3462,7 @@
         <v>180</v>
       </c>
       <c r="F93" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3562,7 +3562,7 @@
         <v>190</v>
       </c>
       <c r="F98" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
@@ -3602,7 +3602,7 @@
         <v>194</v>
       </c>
       <c r="F100" s="19">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -3642,7 +3642,7 @@
         <v>198</v>
       </c>
       <c r="F102" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
@@ -3702,7 +3702,7 @@
         <v>204</v>
       </c>
       <c r="F105" s="19">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -3722,7 +3722,7 @@
         <v>206</v>
       </c>
       <c r="F106" s="19">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
@@ -3742,7 +3742,7 @@
         <v>208</v>
       </c>
       <c r="F107" s="19">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>210</v>
       </c>
       <c r="F108" s="19">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
@@ -3782,7 +3782,7 @@
         <v>212</v>
       </c>
       <c r="F109" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
@@ -3876,7 +3876,7 @@
         <v>220</v>
       </c>
       <c r="F113" s="21">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3976,7 +3976,7 @@
         <v>230</v>
       </c>
       <c r="F118" s="23">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -3996,7 +3996,7 @@
         <v>232</v>
       </c>
       <c r="F119" s="23">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -4016,7 +4016,7 @@
         <v>234</v>
       </c>
       <c r="F120" s="23">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4056,7 +4056,7 @@
         <v>238</v>
       </c>
       <c r="F122" s="23">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -4096,7 +4096,7 @@
         <v>242</v>
       </c>
       <c r="F124" s="23">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -4116,7 +4116,7 @@
         <v>244</v>
       </c>
       <c r="F125" s="23">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -4196,7 +4196,7 @@
         <v>329</v>
       </c>
       <c r="F129" s="25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -4216,7 +4216,7 @@
         <v>330</v>
       </c>
       <c r="F130" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -4236,7 +4236,7 @@
         <v>331</v>
       </c>
       <c r="F131" s="25">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -4256,7 +4256,7 @@
         <v>332</v>
       </c>
       <c r="F132" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
@@ -4276,7 +4276,7 @@
         <v>333</v>
       </c>
       <c r="F133" s="25">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -4336,7 +4336,7 @@
         <v>336</v>
       </c>
       <c r="F136" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/laiton.xlsx
+++ b/prix/laiton.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0445A7C-A85F-4DC5-9F35-9AD48C32332D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094C133D-C35C-4A73-854F-DEE693E43DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23124" yWindow="84" windowWidth="19116" windowHeight="10884" xr2:uid="{2BA8A27F-C677-4342-8A29-D0C4A22FC515}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2BA8A27F-C677-4342-8A29-D0C4A22FC515}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1711,13 +1711,13 @@
         <v>270</v>
       </c>
       <c r="D5" s="16">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>6</v>
       </c>
       <c r="F5" s="17">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1737,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="17">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="17">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1857,7 +1857,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="17">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1871,13 +1871,13 @@
         <v>270</v>
       </c>
       <c r="D13" s="16">
-        <v>0.64</v>
+        <v>1.57</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="17">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1897,7 +1897,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="17">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1997,7 +1997,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2051,13 +2051,13 @@
         <v>273</v>
       </c>
       <c r="D22" s="18">
-        <v>23.04</v>
+        <v>19.95</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>40</v>
       </c>
       <c r="F22" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2157,7 +2157,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2277,7 +2277,7 @@
         <v>62</v>
       </c>
       <c r="F33" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2291,13 +2291,13 @@
         <v>270</v>
       </c>
       <c r="D34" s="18">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="19">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2317,7 +2317,7 @@
         <v>66</v>
       </c>
       <c r="F35" s="19">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2357,7 +2357,7 @@
         <v>70</v>
       </c>
       <c r="F37" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2457,7 +2457,7 @@
         <v>80</v>
       </c>
       <c r="F42" s="19">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2477,7 +2477,7 @@
         <v>82</v>
       </c>
       <c r="F43" s="19">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2497,7 +2497,7 @@
         <v>84</v>
       </c>
       <c r="F44" s="19">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2517,7 +2517,7 @@
         <v>86</v>
       </c>
       <c r="F45" s="19">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2537,7 +2537,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="19">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2557,7 +2557,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2657,7 +2657,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="19">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2677,7 +2677,7 @@
         <v>102</v>
       </c>
       <c r="F53" s="19">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2697,7 +2697,7 @@
         <v>104</v>
       </c>
       <c r="F54" s="19">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2757,7 +2757,7 @@
         <v>110</v>
       </c>
       <c r="F57" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2832,7 +2832,7 @@
         <v>118</v>
       </c>
       <c r="F61" s="19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2852,7 +2852,7 @@
         <v>120</v>
       </c>
       <c r="F62" s="19">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2872,7 +2872,7 @@
         <v>122</v>
       </c>
       <c r="F63" s="19">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2912,7 +2912,7 @@
         <v>126</v>
       </c>
       <c r="F65" s="19">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2932,7 +2932,7 @@
         <v>128</v>
       </c>
       <c r="F66" s="19">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -3021,13 +3021,13 @@
         <v>311</v>
       </c>
       <c r="D71" s="18">
-        <v>1.0900000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>137</v>
       </c>
       <c r="F71" s="19">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3041,13 +3041,13 @@
         <v>307</v>
       </c>
       <c r="D72" s="18">
-        <v>1.6500000000000001</v>
+        <v>2.11</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>139</v>
       </c>
       <c r="F72" s="19">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -3067,7 +3067,7 @@
         <v>141</v>
       </c>
       <c r="F73" s="19">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3087,7 +3087,7 @@
         <v>143</v>
       </c>
       <c r="F74" s="19">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3127,7 +3127,7 @@
         <v>147</v>
       </c>
       <c r="F76" s="19">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3147,7 +3147,7 @@
         <v>149</v>
       </c>
       <c r="F77" s="19">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3227,7 +3227,7 @@
         <v>157</v>
       </c>
       <c r="F81" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3247,7 +3247,7 @@
         <v>159</v>
       </c>
       <c r="F82" s="19">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3422,7 +3422,7 @@
         <v>176</v>
       </c>
       <c r="F91" s="19">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3442,7 +3442,7 @@
         <v>178</v>
       </c>
       <c r="F92" s="19">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3456,13 +3456,13 @@
         <v>309</v>
       </c>
       <c r="D93" s="18">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>180</v>
       </c>
       <c r="F93" s="19">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3602,7 +3602,7 @@
         <v>194</v>
       </c>
       <c r="F100" s="19">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -3622,7 +3622,7 @@
         <v>196</v>
       </c>
       <c r="F101" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
@@ -3642,7 +3642,7 @@
         <v>198</v>
       </c>
       <c r="F102" s="19">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
@@ -3702,7 +3702,7 @@
         <v>204</v>
       </c>
       <c r="F105" s="19">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -3722,7 +3722,7 @@
         <v>206</v>
       </c>
       <c r="F106" s="19">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
@@ -3742,7 +3742,7 @@
         <v>208</v>
       </c>
       <c r="F107" s="19">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>210</v>
       </c>
       <c r="F108" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
@@ -3776,13 +3776,13 @@
         <v>273</v>
       </c>
       <c r="D109" s="18">
-        <v>14.35</v>
+        <v>13.33</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>212</v>
       </c>
       <c r="F109" s="19">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
@@ -3849,7 +3849,7 @@
         <v>218</v>
       </c>
       <c r="F112" s="21">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G112" s="2"/>
       <c r="I112" s="2"/>
@@ -3976,7 +3976,7 @@
         <v>230</v>
       </c>
       <c r="F118" s="23">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -3996,7 +3996,7 @@
         <v>232</v>
       </c>
       <c r="F119" s="23">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -4036,7 +4036,7 @@
         <v>236</v>
       </c>
       <c r="F121" s="23">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -4056,7 +4056,7 @@
         <v>238</v>
       </c>
       <c r="F122" s="23">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -4076,7 +4076,7 @@
         <v>240</v>
       </c>
       <c r="F123" s="23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -4096,7 +4096,7 @@
         <v>242</v>
       </c>
       <c r="F124" s="23">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -4116,7 +4116,7 @@
         <v>244</v>
       </c>
       <c r="F125" s="23">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -4156,7 +4156,7 @@
         <v>248</v>
       </c>
       <c r="F127" s="23">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -4196,7 +4196,7 @@
         <v>329</v>
       </c>
       <c r="F129" s="25">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -4236,7 +4236,7 @@
         <v>331</v>
       </c>
       <c r="F131" s="25">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -4256,7 +4256,7 @@
         <v>332</v>
       </c>
       <c r="F132" s="25">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/laiton.xlsx
+++ b/prix/laiton.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094C133D-C35C-4A73-854F-DEE693E43DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32853F4D-551C-413F-AEED-AF66657AC5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2BA8A27F-C677-4342-8A29-D0C4A22FC515}"/>
   </bookViews>
@@ -1697,7 +1697,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1717,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="17">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1737,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="17">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1877,7 +1877,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="17">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1891,13 +1891,13 @@
         <v>271</v>
       </c>
       <c r="D14" s="16">
-        <v>2.15</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="17">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2017,7 +2017,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2037,7 +2037,7 @@
         <v>38</v>
       </c>
       <c r="F21" s="19">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2277,7 +2277,7 @@
         <v>62</v>
       </c>
       <c r="F33" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2297,7 +2297,7 @@
         <v>64</v>
       </c>
       <c r="F34" s="19">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2317,7 +2317,7 @@
         <v>66</v>
       </c>
       <c r="F35" s="19">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2337,7 +2337,7 @@
         <v>68</v>
       </c>
       <c r="F36" s="19">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2417,7 +2417,7 @@
         <v>76</v>
       </c>
       <c r="F40" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2477,7 +2477,7 @@
         <v>82</v>
       </c>
       <c r="F43" s="19">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2491,13 +2491,13 @@
         <v>270</v>
       </c>
       <c r="D44" s="18">
-        <v>1.26</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>84</v>
       </c>
       <c r="F44" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2517,7 +2517,7 @@
         <v>86</v>
       </c>
       <c r="F45" s="19">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2537,7 +2537,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="19">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2557,7 +2557,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2657,7 +2657,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2677,7 +2677,7 @@
         <v>102</v>
       </c>
       <c r="F53" s="19">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2697,7 +2697,7 @@
         <v>104</v>
       </c>
       <c r="F54" s="19">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2717,7 +2717,7 @@
         <v>106</v>
       </c>
       <c r="F55" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2737,7 +2737,7 @@
         <v>108</v>
       </c>
       <c r="F56" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2852,7 +2852,7 @@
         <v>120</v>
       </c>
       <c r="F62" s="19">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2872,7 +2872,7 @@
         <v>122</v>
       </c>
       <c r="F63" s="19">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2912,7 +2912,7 @@
         <v>126</v>
       </c>
       <c r="F65" s="19">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2932,7 +2932,7 @@
         <v>128</v>
       </c>
       <c r="F66" s="19">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -3027,7 +3027,7 @@
         <v>137</v>
       </c>
       <c r="F71" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3047,7 +3047,7 @@
         <v>139</v>
       </c>
       <c r="F72" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -3067,7 +3067,7 @@
         <v>141</v>
       </c>
       <c r="F73" s="19">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3087,7 +3087,7 @@
         <v>143</v>
       </c>
       <c r="F74" s="19">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3107,7 +3107,7 @@
         <v>145</v>
       </c>
       <c r="F75" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3127,7 +3127,7 @@
         <v>147</v>
       </c>
       <c r="F76" s="19">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3147,7 +3147,7 @@
         <v>149</v>
       </c>
       <c r="F77" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3247,7 +3247,7 @@
         <v>159</v>
       </c>
       <c r="F82" s="19">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3267,7 +3267,7 @@
         <v>161</v>
       </c>
       <c r="F83" s="19">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3307,7 +3307,7 @@
         <v>165</v>
       </c>
       <c r="F85" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3347,7 +3347,7 @@
         <v>169</v>
       </c>
       <c r="F87" s="19">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3422,7 +3422,7 @@
         <v>176</v>
       </c>
       <c r="F91" s="19">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3436,13 +3436,13 @@
         <v>270</v>
       </c>
       <c r="D92" s="18">
-        <v>1.74</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E92" s="11" t="s">
         <v>178</v>
       </c>
       <c r="F92" s="19">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3462,7 +3462,7 @@
         <v>180</v>
       </c>
       <c r="F93" s="19">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3482,7 +3482,7 @@
         <v>182</v>
       </c>
       <c r="F94" s="19">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3502,7 +3502,7 @@
         <v>184</v>
       </c>
       <c r="F95" s="19">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -3582,7 +3582,7 @@
         <v>192</v>
       </c>
       <c r="F99" s="19">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
@@ -3602,7 +3602,7 @@
         <v>194</v>
       </c>
       <c r="F100" s="19">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
@@ -3622,7 +3622,7 @@
         <v>196</v>
       </c>
       <c r="F101" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
@@ -3662,7 +3662,7 @@
         <v>200</v>
       </c>
       <c r="F103" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
@@ -3702,7 +3702,7 @@
         <v>204</v>
       </c>
       <c r="F105" s="19">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
@@ -3722,7 +3722,7 @@
         <v>206</v>
       </c>
       <c r="F106" s="19">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
@@ -3742,7 +3742,7 @@
         <v>208</v>
       </c>
       <c r="F107" s="19">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>210</v>
       </c>
       <c r="F108" s="19">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
@@ -3782,7 +3782,7 @@
         <v>212</v>
       </c>
       <c r="F109" s="19">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
@@ -3822,7 +3822,7 @@
         <v>216</v>
       </c>
       <c r="F111" s="21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G111" s="2"/>
       <c r="I111" s="2"/>
@@ -3876,7 +3876,7 @@
         <v>220</v>
       </c>
       <c r="F113" s="21">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3970,13 +3970,13 @@
         <v>292</v>
       </c>
       <c r="D118" s="22">
-        <v>1.61</v>
+        <v>1.8900000000000001</v>
       </c>
       <c r="E118" s="13" t="s">
         <v>230</v>
       </c>
       <c r="F118" s="23">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -3990,13 +3990,13 @@
         <v>293</v>
       </c>
       <c r="D119" s="22">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="E119" s="13" t="s">
         <v>232</v>
       </c>
       <c r="F119" s="23">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -4016,7 +4016,7 @@
         <v>234</v>
       </c>
       <c r="F120" s="23">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4036,7 +4036,7 @@
         <v>236</v>
       </c>
       <c r="F121" s="23">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -4050,13 +4050,13 @@
         <v>296</v>
       </c>
       <c r="D122" s="22">
-        <v>8.7100000000000009</v>
+        <v>9.68</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>238</v>
       </c>
       <c r="F122" s="23">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -4076,7 +4076,7 @@
         <v>240</v>
       </c>
       <c r="F123" s="23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -4096,7 +4096,7 @@
         <v>242</v>
       </c>
       <c r="F124" s="23">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -4130,13 +4130,13 @@
         <v>300</v>
       </c>
       <c r="D126" s="22">
-        <v>6.9</v>
+        <v>7.67</v>
       </c>
       <c r="E126" s="13" t="s">
         <v>246</v>
       </c>
       <c r="F126" s="23">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -4196,7 +4196,7 @@
         <v>329</v>
       </c>
       <c r="F129" s="25">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -4276,7 +4276,7 @@
         <v>333</v>
       </c>
       <c r="F133" s="25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -4296,7 +4296,7 @@
         <v>334</v>
       </c>
       <c r="F134" s="25">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
